--- a/public/sap-reporting/expansion-150-downloads/EXT-PP17-01.xlsx
+++ b/public/sap-reporting/expansion-150-downloads/EXT-PP17-01.xlsx
@@ -2,9 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Layout" sheetId="1" r:id="R032d4d91cb034798"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Flat input" sheetId="2" r:id="R9c856c14248c43de"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Fields" sheetId="3" r:id="R10da1a80b9414391"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Layout" sheetId="1" r:id="Re729d87b1643464e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Flat input" sheetId="2" r:id="Radced9c94859445f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Fields" sheetId="3" r:id="Rd39f1b5bb4b84ee6"/>
   </x:sheets>
 </x:workbook>
 </file>
